--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T11:02:30+00:00</t>
+    <t>2023-11-06T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,7 +872,7 @@
 </t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-unavailability-reason</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-unavailability-reason</t>
   </si>
   <si>
     <t>Extension.extension:created</t>
@@ -1250,7 +1250,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.3203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:08:49+00:00</t>
+    <t>2023-11-07T10:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:16:09+00:00</t>
+    <t>2023-11-07T10:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:18:25+00:00</t>
+    <t>2023-11-07T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:25:25+00:00</t>
+    <t>2023-11-07T10:39:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:39:28+00:00</t>
+    <t>2023-11-07T10:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:47:16+00:00</t>
+    <t>2023-11-07T10:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
